--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484350_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484350_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.3541</v>
+        <v>3.2105</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1842</v>
+        <v>4.4764</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8300999999999999</v>
+        <v>-1.2659</v>
       </c>
       <c r="G2" t="n">
         <v>4.5003</v>
@@ -610,13 +610,13 @@
         <v>1.5627</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7989000000000001</v>
+        <v>-0.3447</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0347</v>
+        <v>0.3269</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2358</v>
+        <v>-0.6716</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5545</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4739</v>
+        <v>2.1217</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4848</v>
+        <v>1.0509</v>
       </c>
       <c r="F3" t="n">
-        <v>0.989</v>
+        <v>1.0707</v>
       </c>
       <c r="G3" t="n">
         <v>-0.4187</v>
@@ -688,13 +688,13 @@
         <v>2.5395</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5921</v>
+        <v>0.0557</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.839</v>
+        <v>-0.2729</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2469</v>
+        <v>0.3286</v>
       </c>
       <c r="V3" t="n">
         <v>-0.0549</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9543</v>
+        <v>1.6117</v>
       </c>
       <c r="E4" t="n">
-        <v>1.9415</v>
+        <v>2.2448</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9872</v>
+        <v>-0.6331</v>
       </c>
       <c r="G4" t="n">
         <v>3.3924</v>
@@ -766,13 +766,13 @@
         <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4064</v>
+        <v>-0.749</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6987</v>
+        <v>-0.3954</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7077</v>
+        <v>-0.3536</v>
       </c>
       <c r="V4" t="n">
         <v>-1.6177</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5695</v>
+        <v>0.2994</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0566</v>
+        <v>-0.1862</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5129</v>
+        <v>0.4856</v>
       </c>
       <c r="G5" t="n">
         <v>1.7778</v>
@@ -844,13 +844,13 @@
         <v>1.5627</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0511</v>
+        <v>-0.3212</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0359</v>
+        <v>-0.2069</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.1143</v>
       </c>
       <c r="V5" t="n">
         <v>0.2102</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>P. MARTÍNEZ SERRANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1396</v>
+        <v>-0.2365</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4607</v>
+        <v>0.1763</v>
       </c>
       <c r="F6" t="n">
-        <v>0.321</v>
+        <v>-0.4128</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6884</v>
+        <v>0.0517</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06859999999999999</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6198</v>
+        <v>0.1348</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1272</v>
+        <v>0.0614</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0463</v>
+        <v>0.0614</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4388</v>
+        <v>-0.0097</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9777</v>
+        <v>-0.1445</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5389</v>
+        <v>0.1348</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.202</v>
+        <v>-0.2882</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1432</v>
+        <v>0.1149</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3452</v>
+        <v>-0.4031</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1554</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.067</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ SERRANO</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4193</v>
+        <v>-0.2442</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0752</v>
+        <v>0.3507</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4945</v>
+        <v>-0.5949</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0517</v>
+        <v>-1.723</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-1.075</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1348</v>
+        <v>-0.648</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0614</v>
+        <v>0.0045</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0614</v>
+        <v>0.5167</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.5122</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0097</v>
+        <v>-1.7275</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1445</v>
+        <v>-1.5917</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1348</v>
+        <v>-0.1358</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.9534</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.471</v>
+        <v>-0.6617</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0138</v>
+        <v>-0.1181</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4848</v>
+        <v>-0.5436</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.441</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5498</v>
+        <v>-0.2486</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2901</v>
+        <v>-0.4607</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.84</v>
+        <v>0.2121</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.723</v>
+        <v>0.6884</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.075</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.648</v>
+        <v>0.6198</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0045</v>
+        <v>1.1272</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5167</v>
+        <v>1.0463</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5122</v>
+        <v>0.0809</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7275</v>
+        <v>-0.4388</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5917</v>
+        <v>-0.9777</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1358</v>
+        <v>0.5389</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9767</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9534</v>
+        <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9673</v>
+        <v>-0.311</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1786</v>
+        <v>0.1432</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.7887</v>
+        <v>-0.4541</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1638</v>
+        <v>0.1554</v>
       </c>
       <c r="W8" t="n">
-        <v>1.441</v>
+        <v>0.2224</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>-0.067</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6687</v>
+        <v>-0.4954</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8107</v>
+        <v>-1.4468</v>
       </c>
       <c r="F9" t="n">
-        <v>1.1421</v>
+        <v>0.9514</v>
       </c>
       <c r="G9" t="n">
         <v>-1.234</v>
@@ -1156,13 +1156,13 @@
         <v>1.7581</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0708</v>
+        <v>-0.8976</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1362</v>
+        <v>-0.7723</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0653</v>
+        <v>-0.1253</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1219</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1292</v>
+        <v>-3.6127</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3915</v>
+        <v>-0.6219</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7377</v>
+        <v>-2.9908</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.9559</v>
+        <v>-2.5272</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9824000000000001</v>
+        <v>0.5608</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0265</v>
+        <v>-3.088</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1669</v>
+        <v>-0.8599</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6792</v>
+        <v>1.8227</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5122</v>
+        <v>-2.6826</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1228</v>
+        <v>-1.6674</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6615</v>
+        <v>-1.2619</v>
       </c>
       <c r="O10" t="n">
-        <v>0.5387</v>
+        <v>-0.4054</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3482</v>
+        <v>-1.1171</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0359</v>
+        <v>-0.004</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3841</v>
+        <v>-1.1131</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.067</v>
+        <v>-0.5545</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5972</v>
+        <v>-1.7731</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.284</v>
+        <v>-4.2303</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8847</v>
+        <v>-3.4926</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3994</v>
+        <v>-0.7377</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.5272</v>
+        <v>-0.9559</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5608</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.088</v>
+        <v>0.0265</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8599</v>
+        <v>0.1669</v>
       </c>
       <c r="K11" t="n">
-        <v>1.8227</v>
+        <v>0.6792</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.6826</v>
+        <v>-0.5122</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6674</v>
+        <v>-1.1228</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2619</v>
+        <v>-1.6615</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4054</v>
+        <v>0.5387</v>
       </c>
       <c r="P11" t="n">
-        <v>0.586</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.7883</v>
+        <v>-1.4493</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2667</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.5216</v>
+        <v>-1.3841</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.5545</v>
+        <v>-0.067</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2186</v>
+        <v>-0.6642</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7731</v>
+        <v>0.5972</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7203</v>
+        <v>-5.4322</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.218</v>
+        <v>-3.5213</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5023</v>
+        <v>-1.9109</v>
       </c>
       <c r="G12" t="n">
         <v>-0.158</v>
@@ -1390,13 +1390,13 @@
         <v>0.7814</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4031</v>
+        <v>0.6912</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0731</v>
+        <v>0.7698</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3299</v>
+        <v>-0.0786</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8865</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.559100000000001</v>
+        <v>-7.256600000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.733200000000001</v>
+        <v>-1.430399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.8262</v>
+        <v>-5.8263</v>
       </c>
       <c r="G13" t="n">
         <v>3.3938</v>
@@ -1468,10 +1468,10 @@
         <v>15.6274</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.6952</v>
+        <v>-5.3929</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7826000000000002</v>
+        <v>-0.4799999999999998</v>
       </c>
       <c r="U13" t="n">
         <v>-4.9128</v>
@@ -1483,7 +1483,7 @@
         <v>3.3815</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.7092</v>
+        <v>-5.709199999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.678800000000001</v>
+        <v>10.539</v>
       </c>
       <c r="E14" t="n">
-        <v>8.0907</v>
+        <v>9.3041</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5881</v>
+        <v>1.235</v>
       </c>
       <c r="G14" t="n">
         <v>3.9961</v>
@@ -1546,13 +1546,13 @@
         <v>3.3208</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7665999999999999</v>
+        <v>1.0937</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.6111</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1643</v>
+        <v>0.4826</v>
       </c>
       <c r="V14" t="n">
         <v>2.7145</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.5822</v>
+        <v>8.301399999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>7.0929</v>
+        <v>7.0348</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4893</v>
+        <v>1.2666</v>
       </c>
       <c r="G15" t="n">
-        <v>3.8528</v>
+        <v>4.5873</v>
       </c>
       <c r="H15" t="n">
-        <v>1.925</v>
+        <v>2.7521</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9277</v>
+        <v>1.8352</v>
       </c>
       <c r="J15" t="n">
-        <v>4.4364</v>
+        <v>7.153</v>
       </c>
       <c r="K15" t="n">
-        <v>3.5866</v>
+        <v>5.4515</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8498</v>
+        <v>1.7015</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5836</v>
+        <v>-2.5657</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6615</v>
+        <v>-2.6994</v>
       </c>
       <c r="O15" t="n">
-        <v>1.078</v>
+        <v>0.1336</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.5627</v>
+        <v>-3.5162</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3441</v>
+        <v>3.1255</v>
       </c>
       <c r="S15" t="n">
-        <v>4.9443</v>
+        <v>1.7224</v>
       </c>
       <c r="T15" t="n">
-        <v>4.6611</v>
+        <v>1.0155</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2832</v>
+        <v>0.7069</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9962</v>
+        <v>2.3824</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.4418</v>
+        <v>2.3824</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.3282</v>
+        <v>6.4602</v>
       </c>
       <c r="E16" t="n">
-        <v>6.2259</v>
+        <v>4.5651</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1023</v>
+        <v>1.8951</v>
       </c>
       <c r="G16" t="n">
-        <v>4.5873</v>
+        <v>3.8528</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7521</v>
+        <v>1.925</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8352</v>
+        <v>1.9277</v>
       </c>
       <c r="J16" t="n">
-        <v>7.153</v>
+        <v>4.4364</v>
       </c>
       <c r="K16" t="n">
-        <v>5.4515</v>
+        <v>3.5866</v>
       </c>
       <c r="L16" t="n">
-        <v>1.7015</v>
+        <v>0.8498</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.5657</v>
+        <v>-0.5836</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.6994</v>
+        <v>-1.6615</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1336</v>
+        <v>1.078</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3907</v>
+        <v>0.7814</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.5162</v>
+        <v>-1.5627</v>
       </c>
       <c r="R16" t="n">
-        <v>3.1255</v>
+        <v>2.3441</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2509</v>
+        <v>2.8222</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2066</v>
+        <v>2.1332</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4575</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="V16" t="n">
-        <v>2.3824</v>
+        <v>-0.9962</v>
       </c>
       <c r="W16" t="n">
-        <v>2.3824</v>
+        <v>-0.4418</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3054</v>
+        <v>1.3715</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6403</v>
+        <v>-0.8426</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9458</v>
+        <v>2.214</v>
       </c>
       <c r="G17" t="n">
         <v>-2.313</v>
@@ -1780,13 +1780,13 @@
         <v>1.1721</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7003</v>
+        <v>1.7663</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0264</v>
+        <v>0.8242</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.9422</v>
       </c>
       <c r="V17" t="n">
         <v>0.9414</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0307</v>
+        <v>1.1461</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8044</v>
+        <v>0.7033</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2263</v>
+        <v>0.4429</v>
       </c>
       <c r="G18" t="n">
         <v>0.0187</v>
@@ -1858,13 +1858,13 @@
         <v>0.586</v>
       </c>
       <c r="S18" t="n">
-        <v>0.426</v>
+        <v>0.5414</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6411</v>
+        <v>0.54</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2152</v>
+        <v>0.0014</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3466</v>
+        <v>0.3388</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0609</v>
+        <v>0.162</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2857</v>
+        <v>0.1767</v>
       </c>
       <c r="G19" t="n">
         <v>-0.07870000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>0.1953</v>
       </c>
       <c r="S19" t="n">
-        <v>0.23</v>
+        <v>0.2222</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.1011</v>
       </c>
       <c r="U19" t="n">
-        <v>0.23</v>
+        <v>0.121</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>P. BERMEJO JARAMILLO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.2884</v>
+        <v>-0.7368</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7782</v>
+        <v>-0.4563</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.5102</v>
+        <v>-0.2805</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5983000000000001</v>
+        <v>-1.49</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6562</v>
+        <v>-0.9908</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2544</v>
+        <v>-0.4992</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6827</v>
+        <v>-0.5313</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1023</v>
+        <v>-0.5718</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5803</v>
+        <v>0.0405</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0844</v>
+        <v>-0.9587</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7585</v>
+        <v>-0.419</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6741</v>
+        <v>-0.5397</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2774</v>
+        <v>0.1672</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2888</v>
+        <v>0.075</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0115</v>
+        <v>0.0921</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.3593</v>
+        <v>-1.0403</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.585</v>
+        <v>-1.4839</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2257</v>
+        <v>0.4436</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7432</v>
@@ -2092,13 +2092,13 @@
         <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7296</v>
+        <v>-0.4106</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6052</v>
+        <v>-0.5041</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1244</v>
+        <v>0.0935</v>
       </c>
       <c r="V21" t="n">
         <v>0.3321</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. BERMEJO JARAMILLO</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.446</v>
+        <v>-1.1342</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.6771</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6863</v>
+        <v>-0.4571</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.49</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.9908</v>
+        <v>-0.6562</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4992</v>
+        <v>1.2544</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5313</v>
+        <v>0.6827</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5718</v>
+        <v>0.1023</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0405</v>
+        <v>0.5803</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9587</v>
+        <v>-0.0844</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.419</v>
+        <v>-0.7585</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5397</v>
+        <v>0.6741</v>
       </c>
       <c r="P22" t="n">
-        <v>0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R22" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.542</v>
+        <v>-0.1231</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2283</v>
+        <v>-0.1877</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3137</v>
+        <v>0.0646</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.933</v>
+        <v>-1.6701</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.7881</v>
+        <v>-3.3836</v>
       </c>
       <c r="F23" t="n">
-        <v>1.8551</v>
+        <v>1.7135</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3532</v>
@@ -2248,13 +2248,13 @@
         <v>3.3208</v>
       </c>
       <c r="S23" t="n">
-        <v>1.315</v>
+        <v>1.5779</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1323</v>
+        <v>0.5368000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>1.1827</v>
+        <v>1.0411</v>
       </c>
       <c r="V23" t="n">
         <v>0.2772</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2929</v>
+        <v>-5.9268</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.6068</v>
+        <v>-3.2134</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6861</v>
+        <v>-2.7134</v>
       </c>
       <c r="G24" t="n">
         <v>-3.4433</v>
@@ -2326,13 +2326,13 @@
         <v>0.9767</v>
       </c>
       <c r="S24" t="n">
-        <v>0.623</v>
+        <v>-0.011</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8778</v>
+        <v>0.2711</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2548</v>
+        <v>-0.2821</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4959</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.393</v>
+        <v>-6.7189</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.2905</v>
+        <v>-5.886</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.1025</v>
+        <v>-0.8328</v>
       </c>
       <c r="G25" t="n">
         <v>-5.0256</v>
@@ -2404,13 +2404,13 @@
         <v>1.3674</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9767</v>
+        <v>-0.3026</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.5034</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0689</v>
+        <v>0.2008</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6093</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>7.559300000000005</v>
+        <v>10.9299</v>
       </c>
       <c r="E26" t="n">
-        <v>5.826300000000002</v>
+        <v>5.8264</v>
       </c>
       <c r="F26" t="n">
-        <v>1.7332</v>
+        <v>5.103600000000001</v>
       </c>
       <c r="G26" t="n">
         <v>-3.3938</v>
@@ -2461,7 +2461,7 @@
         <v>12.8472</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.0153</v>
+        <v>-2.015300000000001</v>
       </c>
       <c r="M26" t="n">
         <v>-14.2255</v>
@@ -2482,16 +2482,16 @@
         <v>18.5575</v>
       </c>
       <c r="S26" t="n">
-        <v>5.695399999999999</v>
+        <v>9.066000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>4.9129</v>
+        <v>4.912799999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>0.7825000000000001</v>
+        <v>4.1531</v>
       </c>
       <c r="V26" t="n">
-        <v>2.3276</v>
+        <v>2.327599999999999</v>
       </c>
       <c r="W26" t="n">
         <v>5.7091</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484350_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484350_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -626,6 +631,11 @@
       </c>
       <c r="X2" t="n">
         <v>-0.5545</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -636,74 +646,79 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1217</v>
+        <v>1.5349</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0509</v>
+        <v>1.5349</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0707</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.4187</v>
+        <v>1.5349</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.7017</v>
+        <v>1.5349</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2831</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3787</v>
+        <v>1.5349</v>
       </c>
       <c r="K3" t="n">
-        <v>0.825</v>
+        <v>1.5349</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5537</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.7973</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5267</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2706</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5395</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0557</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2729</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3286</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -714,938 +729,994 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6117</v>
+        <v>0.914</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2448</v>
+        <v>0.914</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6331</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3924</v>
+        <v>0.914</v>
       </c>
       <c r="H4" t="n">
-        <v>1.3423</v>
+        <v>0.307</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0501</v>
+        <v>0.607</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6169</v>
+        <v>0.914</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3753</v>
+        <v>0.307</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2416</v>
+        <v>0.607</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2245</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.033</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8085</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.586</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.749</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3954</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3536</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.6177</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6177</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>J. BERTOMEU BALDE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2994</v>
+        <v>0.6977</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1862</v>
+        <v>1.3308</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4856</v>
+        <v>-0.6331</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7778</v>
+        <v>2.4785</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4068</v>
+        <v>1.0353</v>
       </c>
       <c r="I5" t="n">
-        <v>2.1846</v>
+        <v>1.4431</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3415</v>
+        <v>2.7029</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9657</v>
+        <v>2.0683</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3758</v>
+        <v>0.6346000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5638</v>
+        <v>-0.2245</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3725</v>
+        <v>-1.033</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8087</v>
+        <v>0.8085</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.3674</v>
+        <v>0.586</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R5" t="n">
         <v>1.5627</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3212</v>
+        <v>-0.749</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2069</v>
+        <v>-0.3954</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1143</v>
+        <v>-0.3536</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2102</v>
+        <v>-1.6177</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3991</v>
+        <v>-1.6177</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ SERRANO</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2365</v>
+        <v>0.5867</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1763</v>
+        <v>-0.484</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4128</v>
+        <v>1.0707</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0517</v>
+        <v>-1.9536</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-2.2367</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1348</v>
+        <v>0.2831</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0614</v>
+        <v>-0.1563</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0614</v>
+        <v>-0.71</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.5537</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0097</v>
+        <v>-1.7973</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1445</v>
+        <v>-1.5267</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1348</v>
+        <v>-0.2706</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.5395</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.5395</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2882</v>
+        <v>0.0557</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1149</v>
+        <v>-0.2729</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4031</v>
+        <v>0.3286</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.0549</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2442</v>
+        <v>0.2994</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3507</v>
+        <v>-0.1862</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5949</v>
+        <v>0.4856</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.723</v>
+        <v>1.7778</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.075</v>
+        <v>-0.4068</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.648</v>
+        <v>2.1846</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0045</v>
+        <v>2.3415</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5167</v>
+        <v>0.9657</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5122</v>
+        <v>1.3758</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7275</v>
+        <v>-0.5638</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.5917</v>
+        <v>-1.3725</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1358</v>
+        <v>0.8087</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9767</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9534</v>
+        <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6617</v>
+        <v>-0.3212</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1181</v>
+        <v>-0.2069</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5436</v>
+        <v>-0.1143</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1638</v>
+        <v>0.2102</v>
       </c>
       <c r="W7" t="n">
-        <v>1.441</v>
+        <v>0.6093</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2772</v>
+        <v>-0.3991</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>P. MARTINEZ SERRANO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2486</v>
+        <v>-0.2365</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4607</v>
+        <v>0.1763</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2121</v>
+        <v>-0.4128</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6884</v>
+        <v>0.0517</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06859999999999999</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>0.6198</v>
+        <v>0.1348</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1272</v>
+        <v>0.0614</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0463</v>
+        <v>0.0614</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0809</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4388</v>
+        <v>-0.0097</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.9777</v>
+        <v>-0.1445</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5389</v>
+        <v>0.1348</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.311</v>
+        <v>-0.2882</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1432</v>
+        <v>0.1149</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4541</v>
+        <v>-0.4031</v>
       </c>
       <c r="V8" t="n">
-        <v>0.1554</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2224</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.067</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4954</v>
+        <v>-0.2442</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4468</v>
+        <v>0.3507</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9514</v>
+        <v>-0.5949</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.234</v>
+        <v>-1.723</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7608</v>
+        <v>-1.075</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.9949</v>
+        <v>-0.648</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6746</v>
+        <v>0.0045</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4543</v>
+        <v>0.5167</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.1289</v>
+        <v>-0.5122</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5595</v>
+        <v>-1.7275</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6935</v>
+        <v>-1.5917</v>
       </c>
       <c r="O9" t="n">
-        <v>0.134</v>
+        <v>-0.1358</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8976</v>
+        <v>-0.6617</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7723</v>
+        <v>-0.1181</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1253</v>
+        <v>-0.5436</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1219</v>
+        <v>1.1638</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.441</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1219</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6127</v>
+        <v>-0.2486</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6219</v>
+        <v>-0.4607</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.9908</v>
+        <v>0.2121</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.5272</v>
+        <v>0.6884</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5608</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.088</v>
+        <v>0.6198</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.8599</v>
+        <v>1.1272</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8227</v>
+        <v>1.0463</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.6826</v>
+        <v>0.0809</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6674</v>
+        <v>-0.4388</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2619</v>
+        <v>-0.9777</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4054</v>
+        <v>0.5389</v>
       </c>
       <c r="P10" t="n">
-        <v>0.586</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>-1.9534</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1171</v>
+        <v>-0.311</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.004</v>
+        <v>0.1432</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1131</v>
+        <v>-0.4541</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5545</v>
+        <v>0.1554</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2186</v>
+        <v>0.2224</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7731</v>
+        <v>-0.067</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2303</v>
+        <v>-0.4954</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4926</v>
+        <v>-1.4468</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.7377</v>
+        <v>0.9514</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.9559</v>
+        <v>-1.234</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.9824000000000001</v>
+        <v>0.7608</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0265</v>
+        <v>-1.9949</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1669</v>
+        <v>-0.6746</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6792</v>
+        <v>1.4543</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5122</v>
+        <v>-2.1289</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1228</v>
+        <v>-0.5595</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6615</v>
+        <v>-0.6935</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5387</v>
+        <v>0.134</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.7581</v>
+        <v>1.7581</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1721</v>
+        <v>1.7581</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4493</v>
+        <v>-0.8976</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.06519999999999999</v>
+        <v>-0.7723</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3841</v>
+        <v>-0.1253</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.067</v>
+        <v>-0.1219</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.5972</v>
+        <v>-0.1219</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4322</v>
+        <v>-3.6127</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5213</v>
+        <v>-0.6219</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9109</v>
+        <v>-2.9908</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.158</v>
+        <v>-2.5272</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2397</v>
+        <v>0.5608</v>
       </c>
       <c r="I12" t="n">
-        <v>0.08169999999999999</v>
+        <v>-3.088</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9598</v>
+        <v>-0.8599</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1474</v>
+        <v>1.8227</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1875</v>
+        <v>-2.6826</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1178</v>
+        <v>-1.6674</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.387</v>
+        <v>-1.2619</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2692</v>
+        <v>-0.4054</v>
       </c>
       <c r="P12" t="n">
-        <v>-5.0789</v>
+        <v>0.586</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.8603</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7814</v>
+        <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6912</v>
+        <v>-1.1171</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7698</v>
+        <v>-0.004</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0786</v>
+        <v>-1.1131</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.8865</v>
+        <v>-0.5545</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6093</v>
+        <v>1.2186</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4959</v>
+        <v>-1.7731</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.256600000000001</v>
+        <v>-4.2303</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.430399999999999</v>
+        <v>-3.4926</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.8263</v>
+        <v>-0.7377</v>
       </c>
       <c r="G13" t="n">
-        <v>3.3938</v>
+        <v>-0.9559</v>
       </c>
       <c r="H13" t="n">
-        <v>4.743000000000001</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.3491</v>
+        <v>0.0265</v>
       </c>
       <c r="J13" t="n">
-        <v>14.2253</v>
+        <v>0.1669</v>
       </c>
       <c r="K13" t="n">
-        <v>17.5901</v>
+        <v>0.6792</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.364599999999999</v>
+        <v>-0.5122</v>
       </c>
       <c r="M13" t="n">
-        <v>-10.8317</v>
+        <v>-1.1228</v>
       </c>
       <c r="N13" t="n">
-        <v>-12.8469</v>
+        <v>-1.6615</v>
       </c>
       <c r="O13" t="n">
-        <v>2.0154</v>
+        <v>0.5387</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.9302</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q13" t="n">
-        <v>-18.5574</v>
+        <v>-2.9301</v>
       </c>
       <c r="R13" t="n">
-        <v>15.6274</v>
+        <v>1.1721</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.3929</v>
+        <v>-1.4493</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4799999999999998</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.9128</v>
+        <v>-1.3841</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.327599999999999</v>
+        <v>-0.067</v>
       </c>
       <c r="W13" t="n">
-        <v>3.3815</v>
+        <v>-0.6642</v>
       </c>
       <c r="X13" t="n">
-        <v>-5.709199999999999</v>
+        <v>0.5972</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB. CORNELLÀ</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.539</v>
+        <v>-5.4322</v>
       </c>
       <c r="E14" t="n">
-        <v>9.3041</v>
+        <v>-3.5213</v>
       </c>
       <c r="F14" t="n">
-        <v>1.235</v>
+        <v>-1.9109</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9961</v>
+        <v>-0.158</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2031</v>
+        <v>-0.2397</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7929</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>6.2873</v>
+        <v>0.9598</v>
       </c>
       <c r="K14" t="n">
-        <v>4.8977</v>
+        <v>1.1474</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3897</v>
+        <v>-0.1875</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.2913</v>
+        <v>-1.1178</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.6945</v>
+        <v>-1.387</v>
       </c>
       <c r="O14" t="n">
-        <v>0.4033</v>
+        <v>0.2692</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7348</v>
+        <v>-5.0789</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.586</v>
+        <v>-5.8603</v>
       </c>
       <c r="R14" t="n">
-        <v>3.3208</v>
+        <v>0.7814</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0937</v>
+        <v>0.6912</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6111</v>
+        <v>0.7698</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4826</v>
+        <v>-0.0786</v>
       </c>
       <c r="V14" t="n">
-        <v>2.7145</v>
+        <v>-0.8865</v>
       </c>
       <c r="W14" t="n">
-        <v>2.9917</v>
+        <v>0.6093</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB. CORNELLÀ</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.301399999999999</v>
+        <v>-7.256699999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>7.0348</v>
+        <v>-1.430400000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2666</v>
+        <v>-5.8263</v>
       </c>
       <c r="G15" t="n">
-        <v>4.5873</v>
+        <v>3.3939</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7521</v>
+        <v>4.7429</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8352</v>
+        <v>-1.3491</v>
       </c>
       <c r="J15" t="n">
-        <v>7.153</v>
+        <v>14.2252</v>
       </c>
       <c r="K15" t="n">
-        <v>5.4515</v>
+        <v>17.59</v>
       </c>
       <c r="L15" t="n">
-        <v>1.7015</v>
+        <v>-3.364599999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.5657</v>
+        <v>-10.8317</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.6994</v>
+        <v>-12.8469</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1336</v>
+        <v>2.0154</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.3907</v>
+        <v>-2.9302</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.5162</v>
+        <v>-18.5574</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1255</v>
+        <v>15.6274</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7224</v>
+        <v>-5.392899999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>1.0155</v>
+        <v>-0.4799999999999998</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7069</v>
+        <v>-4.9128</v>
       </c>
       <c r="V15" t="n">
-        <v>2.3824</v>
+        <v>-2.3276</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3824</v>
+        <v>3.3815</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
-      </c>
+        <v>-5.7092</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.4602</v>
+        <v>10.539</v>
       </c>
       <c r="E16" t="n">
-        <v>4.5651</v>
+        <v>9.3041</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8951</v>
+        <v>1.235</v>
       </c>
       <c r="G16" t="n">
-        <v>3.8528</v>
+        <v>3.9961</v>
       </c>
       <c r="H16" t="n">
-        <v>1.925</v>
+        <v>2.2031</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9277</v>
+        <v>1.7929</v>
       </c>
       <c r="J16" t="n">
-        <v>4.4364</v>
+        <v>6.2873</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5866</v>
+        <v>4.8977</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8498</v>
+        <v>1.3897</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5836</v>
+        <v>-2.2913</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.6615</v>
+        <v>-2.6945</v>
       </c>
       <c r="O16" t="n">
-        <v>1.078</v>
+        <v>0.4033</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7814</v>
+        <v>2.7348</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.5627</v>
+        <v>-0.586</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3441</v>
+        <v>3.3208</v>
       </c>
       <c r="S16" t="n">
-        <v>2.8222</v>
+        <v>1.0937</v>
       </c>
       <c r="T16" t="n">
-        <v>2.1332</v>
+        <v>0.6111</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.4826</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9962</v>
+        <v>2.7145</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.4418</v>
+        <v>2.9917</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3715</v>
+        <v>8.301399999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8426</v>
+        <v>7.0348</v>
       </c>
       <c r="F17" t="n">
-        <v>2.214</v>
+        <v>1.2666</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.313</v>
+        <v>4.5873</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6815</v>
+        <v>2.7521</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.6315</v>
+        <v>1.8352</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.7486</v>
+        <v>7.153</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3876</v>
+        <v>5.4515</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.361</v>
+        <v>1.7015</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.5643</v>
+        <v>-2.5657</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2939</v>
+        <v>-2.6994</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.2704</v>
+        <v>0.1336</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9767</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1953</v>
+        <v>-3.5162</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>3.1255</v>
       </c>
       <c r="S17" t="n">
-        <v>1.7663</v>
+        <v>1.7224</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8242</v>
+        <v>1.0155</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9422</v>
+        <v>0.7069</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9414</v>
+        <v>2.3824</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2772</v>
+        <v>2.3824</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. RAMON CASTELL</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1461</v>
+        <v>6.4602</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7033</v>
+        <v>4.5651</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4429</v>
+        <v>1.8951</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0187</v>
+        <v>3.8528</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4262</v>
+        <v>1.925</v>
       </c>
       <c r="I18" t="n">
-        <v>0.4449</v>
+        <v>1.9277</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1633</v>
+        <v>4.4364</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1228</v>
+        <v>3.5866</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0405</v>
+        <v>0.8498</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1445</v>
+        <v>-0.5836</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.549</v>
+        <v>-1.6615</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4045</v>
+        <v>1.078</v>
       </c>
       <c r="P18" t="n">
-        <v>0.586</v>
+        <v>0.7814</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.5627</v>
       </c>
       <c r="R18" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="S18" t="n">
-        <v>0.5414</v>
+        <v>2.8222</v>
       </c>
       <c r="T18" t="n">
-        <v>0.54</v>
+        <v>2.1332</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0014</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.9962</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.4418</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. DIAZ KAUFFMANN</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1977,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3388</v>
+        <v>1.5279</v>
       </c>
       <c r="E19" t="n">
-        <v>0.162</v>
+        <v>1.5279</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1767</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.07870000000000001</v>
+        <v>1.5279</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.254</v>
+        <v>0.921</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1753</v>
+        <v>0.607</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0609</v>
+        <v>1.5279</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0205</v>
+        <v>0.921</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0405</v>
+        <v>0.607</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.1397</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2745</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1348</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2222</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1011</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.121</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1952,12 +2038,17 @@
       </c>
       <c r="X19" t="n">
         <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. BERMEJO JARAMILLO</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7368</v>
+        <v>1.3715</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.4563</v>
+        <v>-0.8426</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2805</v>
+        <v>2.214</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.49</v>
+        <v>-2.313</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9908</v>
+        <v>-0.6815</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4992</v>
+        <v>-1.6315</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5313</v>
+        <v>-1.7486</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5718</v>
+        <v>-0.3876</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0405</v>
+        <v>-1.361</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9587</v>
+        <v>-0.5643</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.419</v>
+        <v>-0.2939</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.5397</v>
+        <v>-0.2704</v>
       </c>
       <c r="P20" t="n">
-        <v>0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="R20" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1672</v>
+        <v>1.7663</v>
       </c>
       <c r="T20" t="n">
-        <v>0.075</v>
+        <v>0.8242</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0921</v>
+        <v>0.9422</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.9414</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. ROS FERNANDEZ</t>
+          <t>P. RAMON CASTELL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0403</v>
+        <v>1.1461</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4839</v>
+        <v>0.7033</v>
       </c>
       <c r="F21" t="n">
-        <v>0.4436</v>
+        <v>0.4429</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7432</v>
+        <v>0.0187</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.7432</v>
+        <v>-0.4262</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.4449</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9798</v>
+        <v>0.1633</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.3057</v>
+        <v>0.1228</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6741</v>
+        <v>0.0405</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.7634</v>
+        <v>-0.1445</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.4375</v>
+        <v>-0.549</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6741</v>
+        <v>0.4045</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7814</v>
+        <v>0.586</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4106</v>
+        <v>0.5414</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5041</v>
+        <v>0.54</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0935</v>
+        <v>0.0014</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>P. DIAZ KAUFFMANN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1342</v>
+        <v>0.3388</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.6771</v>
+        <v>0.162</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4571</v>
+        <v>0.1767</v>
       </c>
       <c r="G22" t="n">
-        <v>0.5983000000000001</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6562</v>
+        <v>-0.254</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2544</v>
+        <v>0.1753</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6827</v>
+        <v>0.0609</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1023</v>
+        <v>0.0205</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5803</v>
+        <v>0.0405</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0844</v>
+        <v>-0.1397</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7585</v>
+        <v>-0.2745</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6741</v>
+        <v>0.1348</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7814</v>
+        <v>0.1953</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1231</v>
+        <v>0.2222</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1877</v>
+        <v>0.1011</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0646</v>
+        <v>0.121</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>P. BERMEJO JARAMILLO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.6701</v>
+        <v>-0.7368</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3836</v>
+        <v>-0.4563</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7135</v>
+        <v>-0.2805</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3532</v>
+        <v>-1.49</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5321</v>
+        <v>-0.9908</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.8853</v>
+        <v>-0.4992</v>
       </c>
       <c r="J23" t="n">
-        <v>0.07290000000000001</v>
+        <v>-0.5313</v>
       </c>
       <c r="K23" t="n">
-        <v>3.3615</v>
+        <v>-0.5718</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.2886</v>
+        <v>0.0405</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4261</v>
+        <v>-0.9587</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.8293</v>
+        <v>-0.419</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4033</v>
+        <v>-0.5397</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.4929</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.3208</v>
+        <v>0.586</v>
       </c>
       <c r="S23" t="n">
-        <v>1.5779</v>
+        <v>0.1672</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5368000000000001</v>
+        <v>0.075</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0411</v>
+        <v>0.0921</v>
       </c>
       <c r="V23" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.4996</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2224</v>
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>B. ROS FERNANDEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9268</v>
+        <v>-1.0403</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2134</v>
+        <v>-1.4839</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.7134</v>
+        <v>0.4436</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.4433</v>
+        <v>-1.7432</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.1732</v>
+        <v>-1.7432</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.27</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5311</v>
+        <v>-0.9798</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5311</v>
+        <v>-0.3057</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-0.6741</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.9121</v>
+        <v>-0.7634</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.6421</v>
+        <v>-1.4375</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.27</v>
+        <v>0.6741</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.011</v>
+        <v>-0.4106</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2711</v>
+        <v>-0.5041</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2821</v>
+        <v>0.0935</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.4959</v>
+        <v>0.3321</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.4959</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>G. DI BONAVENTURA</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2475,78 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.7189</v>
+        <v>-1.1342</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.886</v>
+        <v>-0.6771</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.8328</v>
+        <v>-0.4571</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.0256</v>
+        <v>0.5983000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-4.2303</v>
+        <v>-0.6562</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.7953</v>
+        <v>1.2544</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.2339</v>
+        <v>0.6827</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.8995</v>
+        <v>0.1023</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.3344</v>
+        <v>0.5803</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.7917</v>
+        <v>-0.0844</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.3308</v>
+        <v>-0.7585</v>
       </c>
       <c r="O25" t="n">
-        <v>0.5391</v>
+        <v>0.6741</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.7814</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="R25" t="n">
-        <v>1.3674</v>
+        <v>0.7814</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.3026</v>
+        <v>-0.1231</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5034</v>
+        <v>-0.1877</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2008</v>
+        <v>0.0646</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,68 +2558,318 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>10.9299</v>
+        <v>-3.1981</v>
       </c>
       <c r="E26" t="n">
-        <v>5.8264</v>
+        <v>-4.9116</v>
       </c>
       <c r="F26" t="n">
+        <v>1.7135</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-3.8811</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-0.3888</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-3.4923</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.4551</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.4405</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-3.8956</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-2.4261</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-2.8293</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.4033</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-4.4929</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3.3208</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1.5779</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.5368000000000001</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.0411</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.4996</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-0.2224</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>U. FERNANDEZ RUIZ</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-5.9268</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-3.2134</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-2.7134</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-3.4433</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-3.1732</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-1.5311</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1.5311</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-1.9121</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-1.6421</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="P27" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.2711</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-0.2821</v>
+      </c>
+      <c r="V27" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>G. DI BONAVENTURA</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-6.7189</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-5.886</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-0.8328</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-5.0256</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-4.2303</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-0.7953</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-3.2339</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-1.8995</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-1.3344</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-1.7917</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-2.3308</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.5391</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-0.3026</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.5034</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.2008</v>
+      </c>
+      <c r="V28" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484350_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>CB. CORNELLÀ</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>10.9298</v>
+      </c>
+      <c r="E29" t="n">
+        <v>5.826300000000002</v>
+      </c>
+      <c r="F29" t="n">
         <v>5.103600000000001</v>
       </c>
-      <c r="G26" t="n">
-        <v>-3.3938</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-4.7431</v>
-      </c>
-      <c r="I26" t="n">
+      <c r="G29" t="n">
+        <v>-3.393799999999997</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-4.743</v>
+      </c>
+      <c r="I29" t="n">
         <v>1.3491</v>
       </c>
-      <c r="J26" t="n">
-        <v>10.8318</v>
-      </c>
-      <c r="K26" t="n">
+      <c r="J29" t="n">
+        <v>10.8317</v>
+      </c>
+      <c r="K29" t="n">
         <v>12.8472</v>
       </c>
-      <c r="L26" t="n">
-        <v>-2.015300000000001</v>
-      </c>
-      <c r="M26" t="n">
+      <c r="L29" t="n">
+        <v>-2.0153</v>
+      </c>
+      <c r="M29" t="n">
         <v>-14.2255</v>
       </c>
-      <c r="N26" t="n">
+      <c r="N29" t="n">
         <v>-17.59</v>
       </c>
-      <c r="O26" t="n">
+      <c r="O29" t="n">
         <v>3.3647</v>
       </c>
-      <c r="P26" t="n">
+      <c r="P29" t="n">
         <v>2.93</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q29" t="n">
         <v>-15.6274</v>
       </c>
-      <c r="R26" t="n">
+      <c r="R29" t="n">
         <v>18.5575</v>
       </c>
-      <c r="S26" t="n">
+      <c r="S29" t="n">
         <v>9.066000000000001</v>
       </c>
-      <c r="T26" t="n">
-        <v>4.912799999999999</v>
-      </c>
-      <c r="U26" t="n">
+      <c r="T29" t="n">
+        <v>4.9128</v>
+      </c>
+      <c r="U29" t="n">
         <v>4.1531</v>
       </c>
-      <c r="V26" t="n">
+      <c r="V29" t="n">
         <v>2.327599999999999</v>
       </c>
-      <c r="W26" t="n">
+      <c r="W29" t="n">
         <v>5.7091</v>
       </c>
-      <c r="X26" t="n">
+      <c r="X29" t="n">
         <v>-3.3816</v>
       </c>
+      <c r="Y29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
